--- a/data/trans_bre/P16A13-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A13-Edad-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,86</t>
+          <t>-0,01; 2,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,72</t>
+          <t>-2,29; 0,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 2,15</t>
+          <t>-1,14; 1,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 0,96</t>
+          <t>-6,58; 1,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-57,68; —</t>
+          <t>-50,73; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 149,68</t>
+          <t>-88,36; 161,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,77</t>
+          <t>-1,77; 0,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,58</t>
+          <t>-1,85; 1,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,32</t>
+          <t>-1,6; 1,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,33</t>
+          <t>-1,83; 1,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,63; 90,58</t>
+          <t>-77,85; 110,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,91; 112,35</t>
+          <t>-62,32; 93,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,19; 135,62</t>
+          <t>-66,17; 188,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-81,52; 345,12</t>
+          <t>-86,67; 253,86</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,0</t>
+          <t>-2,01; 1,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 2,3</t>
+          <t>-1,38; 2,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,28</t>
+          <t>-1,75; 1,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,77</t>
+          <t>-0,57; 2,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,46; 75,89</t>
+          <t>-62,41; 85,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-40,33; 124,57</t>
+          <t>-38,83; 149,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-67,21; 131,39</t>
+          <t>-68,01; 115,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,96; 272,27</t>
+          <t>-24,82; 240,72</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,77</t>
+          <t>-1,0; 3,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,94</t>
+          <t>-1,87; 3,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,41</t>
+          <t>-2,16; 1,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 3,63</t>
+          <t>-2,63; 3,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,82; 224,36</t>
+          <t>-28,06; 246,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,91; 103,63</t>
+          <t>-29,0; 106,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,11; 109,99</t>
+          <t>-69,76; 97,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,28; 146,51</t>
+          <t>-40,13; 139,07</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,99</t>
+          <t>-1,23; 4,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,24</t>
+          <t>1,23; 7,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 6,26</t>
+          <t>-0,8; 6,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,83</t>
+          <t>-0,75; 5,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,36; 177,91</t>
+          <t>-26,25; 175,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,16; 306,69</t>
+          <t>21,67; 356,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 164,36</t>
+          <t>-12,62; 163,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 70,71</t>
+          <t>-7,87; 79,76</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 6,74</t>
+          <t>-0,79; 6,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 7,8</t>
+          <t>-1,26; 8,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 4,68</t>
+          <t>-2,41; 4,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 4,28</t>
+          <t>-9,21; 4,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 257,17</t>
+          <t>-14,39; 249,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 162,2</t>
+          <t>-13,76; 164,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-35,02; 140,9</t>
+          <t>-32,32; 136,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,87; 37,31</t>
+          <t>-65,33; 34,43</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 3,62</t>
+          <t>-5,04; 3,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 3,57</t>
+          <t>-7,84; 3,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 8,2</t>
+          <t>-0,81; 8,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 11,92</t>
+          <t>2,47; 11,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-53,14; 77,71</t>
+          <t>-51,82; 79,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,48; 39,1</t>
+          <t>-47,41; 32,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 167,74</t>
+          <t>-12,59; 165,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,88; 67,53</t>
+          <t>10,65; 67,18</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,77</t>
+          <t>0,08; 1,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,34</t>
+          <t>0,2; 2,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,07</t>
+          <t>0,18; 1,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,27</t>
+          <t>0,16; 3,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,84; 78,22</t>
+          <t>1,76; 85,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,78; 64,62</t>
+          <t>4,07; 66,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,88; 80,53</t>
+          <t>4,94; 77,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,49; 62,71</t>
+          <t>3,32; 67,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A13-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A13-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-0,62</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-64,99%</t>
+          <t>-54,61%</t>
         </is>
       </c>
     </row>
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,81</t>
+          <t>0,09; 2,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,77</t>
+          <t>-2,16; 0,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,87</t>
+          <t>-1,21; 2,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 1,0</t>
+          <t>-2,81; 1,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,73; —</t>
+          <t>-33,82; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-88,36; 161,28</t>
+          <t>-89,77; 134,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-14,11%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,8</t>
+          <t>-1,8; 0,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,35</t>
+          <t>-1,7; 1,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,45</t>
+          <t>-1,68; 1,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,17</t>
+          <t>-1,63; 1,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-77,85; 110,36</t>
+          <t>-77,62; 83,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,32; 93,82</t>
+          <t>-60,06; 130,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,17; 188,28</t>
+          <t>-68,18; 161,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,67; 253,86</t>
+          <t>-75,97; 291,01</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>85,41%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,13</t>
+          <t>-2,12; 1,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,37</t>
+          <t>-1,31; 2,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,26</t>
+          <t>-1,74; 1,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,7</t>
+          <t>-0,33; 2,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,41; 85,2</t>
+          <t>-64,29; 81,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,83; 149,56</t>
+          <t>-40,17; 157,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-68,01; 115,4</t>
+          <t>-65,76; 116,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,82; 240,72</t>
+          <t>-19,76; 286,81</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>-1,43</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>-23,06%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,55</t>
+          <t>-0,88; 3,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 3,8</t>
+          <t>-1,79; 3,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,1</t>
+          <t>-2,11; 1,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 3,18</t>
+          <t>-3,81; 0,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,06; 246,1</t>
+          <t>-26,22; 260,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,0; 106,18</t>
+          <t>-28,67; 101,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-69,76; 97,28</t>
+          <t>-66,58; 112,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 139,07</t>
+          <t>-48,98; 14,68</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,88</t>
+          <t>2,29</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 4,81</t>
+          <t>-1,19; 4,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,66</t>
+          <t>0,89; 7,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 6,05</t>
+          <t>-0,54; 6,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 5,12</t>
+          <t>-0,38; 4,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 175,94</t>
+          <t>-23,29; 186,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,67; 356,84</t>
+          <t>11,97; 318,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 163,65</t>
+          <t>-7,77; 164,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 79,76</t>
+          <t>-4,35; 71,81</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2,1</t>
+          <t>3,46</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-17,2%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 6,73</t>
+          <t>-0,58; 6,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 8,23</t>
+          <t>-1,11; 8,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1175,27 +1175,27 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 4,02</t>
+          <t>0,23; 6,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 249,88</t>
+          <t>-10,92; 272,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 164,37</t>
+          <t>-14,21; 171,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 136,23</t>
+          <t>-36,11; 124,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,33; 34,43</t>
+          <t>0,54; 69,52</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,9</t>
+          <t>6,85</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 3,9</t>
+          <t>-5,47; 3,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 3,14</t>
+          <t>-7,24; 3,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 8,72</t>
+          <t>-0,59; 8,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 11,71</t>
+          <t>2,41; 11,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-51,82; 79,02</t>
+          <t>-52,97; 73,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-47,41; 32,37</t>
+          <t>-45,88; 39,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 165,55</t>
+          <t>-7,42; 177,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,65; 67,18</t>
+          <t>9,7; 68,55</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,82</t>
+          <t>0,08; 1,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,36</t>
+          <t>0,18; 2,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,95</t>
+          <t>0,22; 2,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,36</t>
+          <t>1,01; 3,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,76; 85,31</t>
+          <t>1,07; 74,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,07; 66,76</t>
+          <t>3,62; 60,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,94; 77,86</t>
+          <t>6,52; 85,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,32; 67,03</t>
+          <t>15,02; 54,54</t>
         </is>
       </c>
     </row>
